--- a/import-templates/import-template-companies.xlsx
+++ b/import-templates/import-template-companies.xlsx
@@ -150,8 +150,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1" style="3"/>
+    <col min="2" max="2" width="18" customWidth="1" style="3"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1" style="3"/>
@@ -168,12 +168,12 @@
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">tax_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">customer_code</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tax_id</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -218,8 +218,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -236,12 +236,12 @@
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">tax_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">customer_code</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tax_id</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -278,27 +278,27 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">บริษัท ไทยรุ่งเรือง จำกัด</t>
+          <t xml:space="preserve">บริษัท ไทยรุ่งเรือง ปิโตรเลียม จำกัด</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">C-00142</t>
+          <t xml:space="preserve">0105536000123</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">0105536000123</t>
+          <t xml:space="preserve">GS20260012</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">โรงงาน, PTT</t>
+          <t xml:space="preserve">PT, โรงงาน</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">โรงงานอุตสาหกรรม</t>
+          <t xml:space="preserve">สถานีบริการน้ำมัน</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
@@ -308,7 +308,7 @@
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://thairungruang.co.th</t>
+          <t xml:space="preserve">https://example.co.th</t>
         </is>
       </c>
       <c r="H2" s="9" t="inlineStr">
@@ -325,27 +325,23 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">บริษัท เอ็นเนอร์ยี่ พลัส จำกัด</t>
+          <t xml:space="preserve">ห้างหุ้นส่วนจำกัด เอ็นเนอร์ยี่ พลัส</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">C-00187</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
           <t xml:space="preserve">0105551000456</t>
         </is>
       </c>
+      <c r="C3" s="9"/>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">โรงงาน</t>
+          <t xml:space="preserve">Shell, ตึกแถว</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">พลังงานทดแทน</t>
+          <t xml:space="preserve">จำหน่าย-ติดตั้ง-ซ่อม</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
@@ -359,32 +355,36 @@
           <t xml:space="preserve">45 ซ.ลาดพร้าว 101 แขวงคลองจั่น เขตบางกะปิ กรุงเทพฯ 10240</t>
         </is>
       </c>
-      <c r="I3" s="9"/>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ไม่มีรหัสลูกค้าเดิม เว้นว่างได้</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">โรงแรมสุขสบาย ระยอง</t>
+          <t xml:space="preserve">บริษัท สุขสบาย เซอร์วิส จำกัด</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">C-00203</t>
+          <t xml:space="preserve">0215559000789</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">0215559000789</t>
+          <t xml:space="preserve">CD00812</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">โรงแรม</t>
+          <t xml:space="preserve">Caltex, บริษัท</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">โรงแรม</t>
+          <t xml:space="preserve">บริการหลังการขาย</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -467,86 +467,66 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">นำเข้าไฟล์นี้เป็นอันดับแรก — ผู้ติดต่อ ไซต์งาน และสัญญาบริการ ล้วนอ้างถึงลูกค้าด้วย customer_code</t>
+          <t xml:space="preserve">นำเข้าไฟล์นี้เป็นอันดับแรก — ผู้ติดต่อ ไซต์งาน และสัญญาบริการ ล้วนอ้างถึงลูกค้าในไฟล์นี้</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">customer_code ต้องไม่ซ้ำกันในไฟล์ ระบบไม่ได้บังคับความไม่ซ้ำให้ ถ้าซ้ำการจับคู่ของไฟล์อื่นจะได้บริษัทผิดตัว</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+          <t xml:space="preserve">customer_code และ tax_id ต้องไม่ซ้ำกันในไฟล์ ระบบไม่ได้บังคับความไม่ซ้ำให้ ถ้าซ้ำการจับคู่ของไฟล์อื่นจะได้บริษัทผิดตัว</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ในระบบตอนนี้มีลูกค้าอยู่แล้ว 31 ราย — ถ้าแถวไหนเป็นลูกค้าเดิม ให้กรอก tax_id หรือชื่อให้ตรงของเดิม จะได้ไม่เกิดข้อมูลซ้ำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">คอลัมน์</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">ชื่อหัวคอลัมน์</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">จำเป็น</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">ชนิดข้อมูล</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">คำอธิบาย</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ใช่</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ข้อความ</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ชื่อลูกค้า/นิติบุคคล เช่น “บริษัท ไทยรุ่งเรือง จำกัด” — ถ้าเว้นว่างแถวนั้นจะถูกข้าม</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">customer_code</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">แนะนำ</t>
+          <t xml:space="preserve">ใช่</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -556,14 +536,14 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">รหัสลูกค้า (รหัสเดิมจาก Venio) — เป็นกุญแจที่เทมเพลตผู้ติดต่อ ไซต์งาน และสัญญาใช้อ้างถึงลูกค้ารายนี้ ควรกรอกทุกแถว</t>
+          <t xml:space="preserve">ชื่อลูกค้า/นิติบุคคล เช่น “บริษัท ไทยรุ่งเรือง จำกัด” — ถ้าเว้นว่างแถวนั้นจะถูกข้าม</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -573,7 +553,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">แนะนำ</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -583,19 +563,19 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">เลขประจำตัวผู้เสียภาษี 13 หลัก — ตั้งรูปแบบช่องเป็น Text ไว้แล้ว เลข 0 นำหน้าจะไม่หาย</t>
+          <t xml:space="preserve">เลขประจำตัวผู้เสียภาษี 13 หลัก — กุญแจหลักที่ไฟล์อื่นใช้อ้างถึงลูกค้ารายนี้ (ในระบบตอนนี้ลูกค้าเดิมกรอก tax_id ไว้ 26 จาก 31 ราย จึงเชื่อถือได้กว่า customer_code) · ตั้งรูปแบบช่องเป็น Text ไว้แล้ว เลข 0 นำหน้าจะไม่หาย</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">tags</t>
+          <t xml:space="preserve">customer_code</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -605,24 +585,24 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ข้อความ คั่นด้วย ,</t>
+          <t xml:space="preserve">ข้อความ</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">แท็กสำหรับกรองในหน้ารายชื่อ ใส่ได้หลายอันคั่นด้วยจุลภาค เช่น “Shell, โรงงาน” · ที่ใช้กันบ่อย: Shell / PTT / BCP / บ้าน / โรงงาน / โรงแรม (พิมพ์แท็กใหม่เองได้)</t>
+          <t xml:space="preserve">รหัสลูกค้า — ถ้ามีให้กรอก ระบบจะใช้จับคู่ก่อน tax_id · รูปแบบให้ยึดตามที่ใช้อยู่เดิม เช่น GS20260001, CD00736, L20260001 (ระบบไม่ได้บังคับรูปแบบ) · ปัจจุบันลูกค้าเดิมมีรหัสแค่ 4 จาก 31 ราย</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">E</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">industry</t>
+          <t xml:space="preserve">tags</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -632,24 +612,24 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ข้อความ</t>
+          <t xml:space="preserve">ข้อความ คั่นด้วย ,</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ประเภทธุรกิจ เช่น โรงงานอุตสาหกรรม, ค้าปลีก</t>
+          <t xml:space="preserve">แท็กสำหรับกรองในหน้ารายชื่อ ใส่ได้หลายอันคั่นด้วยจุลภาค เช่น “PT, โรงงาน” · แท็กที่ใช้อยู่จริงในระบบ: PT / PTT / Shell / Caltex / BCP / โรงงาน / ตึกแถว / บริษัท / จำหน่าย-ติดตั้ง-ซ่อม (พิมพ์แท็กใหม่เองได้)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">F</t>
+          <t xml:space="preserve">E</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">phone</t>
+          <t xml:space="preserve">industry</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -664,19 +644,19 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">เบอร์โทรหลักของบริษัท</t>
+          <t xml:space="preserve">ประเภทธุรกิจ เช่น โรงงานอุตสาหกรรม, ค้าปลีก</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">F</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">website</t>
+          <t xml:space="preserve">phone</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -686,24 +666,24 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL</t>
+          <t xml:space="preserve">ข้อความ</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">เว็บไซต์บริษัท</t>
+          <t xml:space="preserve">เบอร์โทรหลักของบริษัท</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">H</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">address</t>
+          <t xml:space="preserve">website</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -713,37 +693,64 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ข้อความ</t>
+          <t xml:space="preserve">URL</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ที่อยู่จดทะเบียน/ที่อยู่ออกใบกำกับภาษี (คนละอันกับที่อยู่ไซต์งาน ซึ่งอยู่ในเทมเพลตไซต์งาน)</t>
+          <t xml:space="preserve">เว็บไซต์บริษัท</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">H</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">address</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ข้อความ</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ที่อยู่จดทะเบียน/ที่อยู่ออกใบกำกับภาษี (คนละอันกับที่อยู่ไซต์งาน ซึ่งอยู่ในเทมเพลตไซต์งาน)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">I</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ข้อความ</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">หมายเหตุ เช่น เงื่อนไขเครดิต ผู้ดูแลหลัก</t>
         </is>
